--- a/Client/Tables/G_ObjInfoTable.xlsx
+++ b/Client/Tables/G_ObjInfoTable.xlsx
@@ -25674,7 +25674,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -35385,9 +35384,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -45130,9 +45126,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -54882,9 +54875,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
